--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/22.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/22.xlsx
@@ -426,13 +426,13 @@
         <v>-10.48707862477851</v>
       </c>
       <c r="E2">
-        <v>-16.85789414204361</v>
+        <v>-24.0420056905061</v>
       </c>
       <c r="F2">
-        <v>-3.691652612519616</v>
+        <v>-3.397395801860162</v>
       </c>
       <c r="G2">
-        <v>-13.55630111070129</v>
+        <v>-16.66474281061828</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.15986284124305</v>
       </c>
       <c r="E3">
-        <v>-17.66652563169727</v>
+        <v>-24.33852564005435</v>
       </c>
       <c r="F3">
-        <v>-3.579134639829957</v>
+        <v>-3.371089338249458</v>
       </c>
       <c r="G3">
-        <v>-13.3845334553962</v>
+        <v>-15.91953073336449</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.707150025141337</v>
       </c>
       <c r="E4">
-        <v>-19.04413270957067</v>
+        <v>-24.42866038670302</v>
       </c>
       <c r="F4">
-        <v>-3.353130332956765</v>
+        <v>-3.36103544308168</v>
       </c>
       <c r="G4">
-        <v>-12.80842901010669</v>
+        <v>-15.47166689062972</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.167414791222479</v>
       </c>
       <c r="E5">
-        <v>-18.65088002674457</v>
+        <v>-25.46218495252561</v>
       </c>
       <c r="F5">
-        <v>-3.483189813768107</v>
+        <v>-3.258836443128694</v>
       </c>
       <c r="G5">
-        <v>-13.08055585343478</v>
+        <v>-15.71033901601071</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.540807695635174</v>
       </c>
       <c r="E6">
-        <v>-19.80282871634175</v>
+        <v>-24.78202627046955</v>
       </c>
       <c r="F6">
-        <v>-3.33466188171135</v>
+        <v>-3.167694491268276</v>
       </c>
       <c r="G6">
-        <v>-13.14608810238466</v>
+        <v>-15.84751809152149</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.839139319820687</v>
       </c>
       <c r="E7">
-        <v>-19.55070592596471</v>
+        <v>-25.60264010234751</v>
       </c>
       <c r="F7">
-        <v>-3.109449494075234</v>
+        <v>-3.130292874664475</v>
       </c>
       <c r="G7">
-        <v>-12.37471774955231</v>
+        <v>-15.64153925861358</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.079674750949441</v>
       </c>
       <c r="E8">
-        <v>-20.36325454563501</v>
+        <v>-26.60780736393407</v>
       </c>
       <c r="F8">
-        <v>-3.111229655623851</v>
+        <v>-3.135065099272003</v>
       </c>
       <c r="G8">
-        <v>-12.00712139396272</v>
+        <v>-15.36544969227498</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.27229242626868</v>
       </c>
       <c r="E9">
-        <v>-20.82030437028116</v>
+        <v>-26.42061836235301</v>
       </c>
       <c r="F9">
-        <v>-3.129531605021303</v>
+        <v>-3.002987715467442</v>
       </c>
       <c r="G9">
-        <v>-11.84343146977346</v>
+        <v>-15.26651072828832</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.417354208302323</v>
       </c>
       <c r="E10">
-        <v>-21.3458881205594</v>
+        <v>-27.39939820589687</v>
       </c>
       <c r="F10">
-        <v>-3.081602267095323</v>
+        <v>-3.123177198674428</v>
       </c>
       <c r="G10">
-        <v>-11.94583326439419</v>
+        <v>-15.04457341060835</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.529456431739126</v>
       </c>
       <c r="E11">
-        <v>-22.27164406194745</v>
+        <v>-27.40876761861874</v>
       </c>
       <c r="F11">
-        <v>-3.148738131622612</v>
+        <v>-3.037676428827074</v>
       </c>
       <c r="G11">
-        <v>-10.9709934721727</v>
+        <v>-14.85973406624145</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.606699340203727</v>
       </c>
       <c r="E12">
-        <v>-22.85516510867982</v>
+        <v>-28.63605653028153</v>
       </c>
       <c r="F12">
-        <v>-2.991355780397331</v>
+        <v>-2.686166176755729</v>
       </c>
       <c r="G12">
-        <v>-10.13898054615199</v>
+        <v>-14.54764066189051</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.640090980971878</v>
       </c>
       <c r="E13">
-        <v>-22.9023246369957</v>
+        <v>-29.29918362159474</v>
       </c>
       <c r="F13">
-        <v>-2.777922777229024</v>
+        <v>-2.766330603794248</v>
       </c>
       <c r="G13">
-        <v>-10.88690561547521</v>
+        <v>-14.3806004656155</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.641930537547114</v>
       </c>
       <c r="E14">
-        <v>-23.99221511879176</v>
+        <v>-30.14986652088363</v>
       </c>
       <c r="F14">
-        <v>-2.866521641162849</v>
+        <v>-2.591970034281189</v>
       </c>
       <c r="G14">
-        <v>-10.22298563921099</v>
+        <v>-13.79287766075592</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.6196277251327628</v>
       </c>
       <c r="E15">
-        <v>-25.19933873569839</v>
+        <v>-30.70635484202721</v>
       </c>
       <c r="F15">
-        <v>-2.913564625967832</v>
+        <v>-2.545287389296423</v>
       </c>
       <c r="G15">
-        <v>-9.157191918843569</v>
+        <v>-13.3873739034689</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.4174498760095017</v>
       </c>
       <c r="E16">
-        <v>-25.53738026342297</v>
+        <v>-30.97394689961446</v>
       </c>
       <c r="F16">
-        <v>-2.60667355568088</v>
+        <v>-2.409523770549403</v>
       </c>
       <c r="G16">
-        <v>-9.137626594706475</v>
+        <v>-13.28239319387307</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.434324653435102</v>
       </c>
       <c r="E17">
-        <v>-26.43276372964158</v>
+        <v>-31.79331087266631</v>
       </c>
       <c r="F17">
-        <v>-2.510061065492374</v>
+        <v>-2.099095571452497</v>
       </c>
       <c r="G17">
-        <v>-9.125172322387737</v>
+        <v>-13.14759109005949</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.399701267886975</v>
       </c>
       <c r="E18">
-        <v>-26.66528275603942</v>
+        <v>-32.16733339061883</v>
       </c>
       <c r="F18">
-        <v>-2.335830549661554</v>
+        <v>-1.79849098138539</v>
       </c>
       <c r="G18">
-        <v>-7.637227766489067</v>
+        <v>-12.7479950012873</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.289162019884345</v>
       </c>
       <c r="E19">
-        <v>-28.01879382371801</v>
+        <v>-33.29140252998778</v>
       </c>
       <c r="F19">
-        <v>-2.177406112243551</v>
+        <v>-1.874135007506832</v>
       </c>
       <c r="G19">
-        <v>-7.444262688096028</v>
+        <v>-12.41036570391919</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.068713172015501</v>
       </c>
       <c r="E20">
-        <v>-28.33964073563546</v>
+        <v>-34.41204361453293</v>
       </c>
       <c r="F20">
-        <v>-1.954091514327249</v>
+        <v>-1.941097743246936</v>
       </c>
       <c r="G20">
-        <v>-6.770258790119189</v>
+        <v>-11.6769606873312</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.717378387168261</v>
       </c>
       <c r="E21">
-        <v>-28.95485204347351</v>
+        <v>-34.18759432881676</v>
       </c>
       <c r="F21">
-        <v>-1.787466239621531</v>
+        <v>-1.656500524871527</v>
       </c>
       <c r="G21">
-        <v>-7.642908662634456</v>
+        <v>-11.53239247417677</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.231195814819118</v>
       </c>
       <c r="E22">
-        <v>-28.51727918553434</v>
+        <v>-34.80580348644789</v>
       </c>
       <c r="F22">
-        <v>-1.78448328860405</v>
+        <v>-1.60700971439127</v>
       </c>
       <c r="G22">
-        <v>-7.317826332860183</v>
+        <v>-11.62518706564254</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.606872250614058</v>
       </c>
       <c r="E23">
-        <v>-29.89537081012656</v>
+        <v>-35.15341820822468</v>
       </c>
       <c r="F23">
-        <v>-1.655844457888509</v>
+        <v>-1.575176383469088</v>
       </c>
       <c r="G23">
-        <v>-7.142102575635668</v>
+        <v>-11.1904164305156</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.85327696747656</v>
       </c>
       <c r="E24">
-        <v>-30.59183652708424</v>
+        <v>-35.89918995017787</v>
       </c>
       <c r="F24">
-        <v>-1.853247723445243</v>
+        <v>-1.319682197056234</v>
       </c>
       <c r="G24">
-        <v>-7.25978584846568</v>
+        <v>-10.83057999367005</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.993426742220465</v>
       </c>
       <c r="E25">
-        <v>-30.47274671763052</v>
+        <v>-35.73315345068664</v>
       </c>
       <c r="F25">
-        <v>-1.563392028796862</v>
+        <v>-1.329480955063949</v>
       </c>
       <c r="G25">
-        <v>-7.00809169220597</v>
+        <v>-11.58988009746622</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.049847209445558</v>
       </c>
       <c r="E26">
-        <v>-30.37631739211119</v>
+        <v>-35.653076444809</v>
       </c>
       <c r="F26">
-        <v>-1.295556824817101</v>
+        <v>-1.259481424425182</v>
       </c>
       <c r="G26">
-        <v>-7.095973434091463</v>
+        <v>-11.27613307561841</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.046236822689687</v>
       </c>
       <c r="E27">
-        <v>-30.45819220216987</v>
+        <v>-35.43395490876285</v>
       </c>
       <c r="F27">
-        <v>-1.395741235246479</v>
+        <v>-1.334373292944883</v>
       </c>
       <c r="G27">
-        <v>-7.319150551075891</v>
+        <v>-11.99281321614199</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.009051985561308</v>
       </c>
       <c r="E28">
-        <v>-30.92406575841997</v>
+        <v>-37.12119639691071</v>
       </c>
       <c r="F28">
-        <v>-1.438586054054075</v>
+        <v>-1.256375875032087</v>
       </c>
       <c r="G28">
-        <v>-7.138321932629821</v>
+        <v>-12.09396693509442</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.958571085824239</v>
       </c>
       <c r="E29">
-        <v>-30.27639661313195</v>
+        <v>-36.50140906608791</v>
       </c>
       <c r="F29">
-        <v>-1.120250259730044</v>
+        <v>-1.286609628499463</v>
       </c>
       <c r="G29">
-        <v>-7.366696606110904</v>
+        <v>-11.33685510189972</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.906130643479599</v>
       </c>
       <c r="E30">
-        <v>-29.46575221678187</v>
+        <v>-36.14126179249489</v>
       </c>
       <c r="F30">
-        <v>-1.123243979523762</v>
+        <v>-1.090212000969729</v>
       </c>
       <c r="G30">
-        <v>-7.60146394302832</v>
+        <v>-11.51875633710051</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.858748562654286</v>
       </c>
       <c r="E31">
-        <v>-30.31572188141456</v>
+        <v>-36.03613100416982</v>
       </c>
       <c r="F31">
-        <v>-1.180003713963584</v>
+        <v>-1.319437828672408</v>
       </c>
       <c r="G31">
-        <v>-7.843832292503903</v>
+        <v>-12.21623531349632</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.817467243670555</v>
       </c>
       <c r="E32">
-        <v>-29.34376191972624</v>
+        <v>-35.0684164868637</v>
       </c>
       <c r="F32">
-        <v>-1.488898604997908</v>
+        <v>-1.307126632332002</v>
       </c>
       <c r="G32">
-        <v>-7.848897427178988</v>
+        <v>-11.81989349098924</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.774225053646332</v>
       </c>
       <c r="E33">
-        <v>-29.51372007770812</v>
+        <v>-35.72104657542713</v>
       </c>
       <c r="F33">
-        <v>-1.454575201662911</v>
+        <v>-1.481328983671127</v>
       </c>
       <c r="G33">
-        <v>-7.939202488399228</v>
+        <v>-11.72972747268165</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.715814864574493</v>
       </c>
       <c r="E34">
-        <v>-28.87215305114543</v>
+        <v>-34.75478569827747</v>
       </c>
       <c r="F34">
-        <v>-1.312028910621769</v>
+        <v>-1.366687076960689</v>
       </c>
       <c r="G34">
-        <v>-8.293460656011097</v>
+        <v>-12.14817049720891</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.628747392249695</v>
       </c>
       <c r="E35">
-        <v>-28.86824950655082</v>
+        <v>-34.17871399128772</v>
       </c>
       <c r="F35">
-        <v>-1.447822350595289</v>
+        <v>-1.252895903572926</v>
       </c>
       <c r="G35">
-        <v>-7.943224801229442</v>
+        <v>-11.82501821548403</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.496769065169441</v>
       </c>
       <c r="E36">
-        <v>-28.07915385376624</v>
+        <v>-34.46282365781794</v>
       </c>
       <c r="F36">
-        <v>-1.26986666655408</v>
+        <v>-1.318155515932874</v>
       </c>
       <c r="G36">
-        <v>-8.034734901025976</v>
+        <v>-11.50251480068485</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.300665509511325</v>
       </c>
       <c r="E37">
-        <v>-27.93352265815357</v>
+        <v>-34.02583497302577</v>
       </c>
       <c r="F37">
-        <v>-1.658573100113331</v>
+        <v>-1.150406146661558</v>
       </c>
       <c r="G37">
-        <v>-8.483075462318395</v>
+        <v>-12.27270328875967</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.026309193071124</v>
       </c>
       <c r="E38">
-        <v>-27.76517663691843</v>
+        <v>-33.15039490633694</v>
       </c>
       <c r="F38">
-        <v>-1.577680538127751</v>
+        <v>-1.11990565889048</v>
       </c>
       <c r="G38">
-        <v>-8.943674973742734</v>
+        <v>-12.37201303384673</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.664594539077186</v>
       </c>
       <c r="E39">
-        <v>-26.95753235459843</v>
+        <v>-32.38275742763771</v>
       </c>
       <c r="F39">
-        <v>-1.367552720896614</v>
+        <v>-1.321495493300962</v>
       </c>
       <c r="G39">
-        <v>-8.411580920852295</v>
+        <v>-12.09006380190362</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.202123293705797</v>
       </c>
       <c r="E40">
-        <v>-25.80668408418512</v>
+        <v>-32.92520747935752</v>
       </c>
       <c r="F40">
-        <v>-1.386923264243678</v>
+        <v>-1.181408625078732</v>
       </c>
       <c r="G40">
-        <v>-8.769394614373342</v>
+        <v>-11.985606158503</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.634627798881641</v>
       </c>
       <c r="E41">
-        <v>-25.71022758782174</v>
+        <v>-31.82413393099952</v>
       </c>
       <c r="F41">
-        <v>-1.225809946236188</v>
+        <v>-1.150568506672506</v>
       </c>
       <c r="G41">
-        <v>-8.693821480802859</v>
+        <v>-12.07384874985227</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.969199942700468</v>
       </c>
       <c r="E42">
-        <v>-24.51029065916528</v>
+        <v>-31.34805319433612</v>
       </c>
       <c r="F42">
-        <v>-1.33533419913213</v>
+        <v>-1.175858563479975</v>
       </c>
       <c r="G42">
-        <v>-8.567871775761287</v>
+        <v>-11.91561460471172</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.206130706960237</v>
       </c>
       <c r="E43">
-        <v>-25.07866396034199</v>
+        <v>-30.25416633422829</v>
       </c>
       <c r="F43">
-        <v>-1.367731648255619</v>
+        <v>-0.8671807047051842</v>
       </c>
       <c r="G43">
-        <v>-8.700349876606301</v>
+        <v>-12.0064957008558</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.354996831685482</v>
       </c>
       <c r="E44">
-        <v>-23.82987838256479</v>
+        <v>-30.45758991512685</v>
       </c>
       <c r="F44">
-        <v>-1.160428563868029</v>
+        <v>-0.9487782073505467</v>
       </c>
       <c r="G44">
-        <v>-9.002692069071321</v>
+        <v>-12.11697853713789</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.4389699784214509</v>
       </c>
       <c r="E45">
-        <v>-24.32737653704746</v>
+        <v>-28.86315497329219</v>
       </c>
       <c r="F45">
-        <v>-1.397663047620974</v>
+        <v>-0.9472241901028948</v>
       </c>
       <c r="G45">
-        <v>-8.313419935067364</v>
+        <v>-12.44562301391242</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.5297292127762909</v>
       </c>
       <c r="E46">
-        <v>-22.18436678239762</v>
+        <v>-29.88029099168102</v>
       </c>
       <c r="F46">
-        <v>-1.375092520996895</v>
+        <v>-0.9692372254648889</v>
       </c>
       <c r="G46">
-        <v>-8.478579741476064</v>
+        <v>-12.63346336781067</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.531713573309319</v>
       </c>
       <c r="E47">
-        <v>-22.25793637112623</v>
+        <v>-29.3446811999498</v>
       </c>
       <c r="F47">
-        <v>-1.221655683711149</v>
+        <v>-0.9755411014001931</v>
       </c>
       <c r="G47">
-        <v>-9.108271987409758</v>
+        <v>-12.26861145447313</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.534863087296469</v>
       </c>
       <c r="E48">
-        <v>-21.09480235073011</v>
+        <v>-28.9968853392127</v>
       </c>
       <c r="F48">
-        <v>-1.352008406583082</v>
+        <v>-0.8956434086653752</v>
       </c>
       <c r="G48">
-        <v>-8.988499760344466</v>
+        <v>-12.11676997276892</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.520101475418779</v>
       </c>
       <c r="E49">
-        <v>-21.41628324900863</v>
+        <v>-27.32937441231626</v>
       </c>
       <c r="F49">
-        <v>-1.384902047780847</v>
+        <v>-0.9413328411341847</v>
       </c>
       <c r="G49">
-        <v>-8.807684384080552</v>
+        <v>-12.40629704345142</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.465592143498712</v>
       </c>
       <c r="E50">
-        <v>-21.03423401087752</v>
+        <v>-26.92048490874168</v>
       </c>
       <c r="F50">
-        <v>-1.422402240105581</v>
+        <v>-1.019855443980356</v>
       </c>
       <c r="G50">
-        <v>-9.169626327889072</v>
+        <v>-12.58284843706075</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.339874600391817</v>
       </c>
       <c r="E51">
-        <v>-20.20492098043082</v>
+        <v>-27.76166706956248</v>
       </c>
       <c r="F51">
-        <v>-1.495073255618376</v>
+        <v>-0.9793681588011268</v>
       </c>
       <c r="G51">
-        <v>-9.099254061360783</v>
+        <v>-12.60284082157241</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.125435809275144</v>
       </c>
       <c r="E52">
-        <v>-19.61365171467132</v>
+        <v>-26.25087304264949</v>
       </c>
       <c r="F52">
-        <v>-1.19243916541441</v>
+        <v>-0.9719642109549048</v>
       </c>
       <c r="G52">
-        <v>-9.141718428993014</v>
+        <v>-12.02392572312006</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.806424275068109</v>
       </c>
       <c r="E53">
-        <v>-19.49683972764347</v>
+        <v>-25.58642816540005</v>
       </c>
       <c r="F53">
-        <v>-1.382614097014315</v>
+        <v>-0.8362014205752883</v>
       </c>
       <c r="G53">
-        <v>-9.5861194410937</v>
+        <v>-12.3846891127166</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.362800868800517</v>
       </c>
       <c r="E54">
-        <v>-18.54243665968289</v>
+        <v>-25.55639532578118</v>
       </c>
       <c r="F54">
-        <v>-1.615164163104429</v>
+        <v>-0.6962479195049091</v>
       </c>
       <c r="G54">
-        <v>-8.900025430807444</v>
+        <v>-12.36764642428043</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.788315503212333</v>
       </c>
       <c r="E55">
-        <v>-18.62111889556617</v>
+        <v>-25.74953474220832</v>
       </c>
       <c r="F55">
-        <v>-1.518658532310883</v>
+        <v>-1.004954771138798</v>
       </c>
       <c r="G55">
-        <v>-8.959168326866523</v>
+        <v>-12.57305584335559</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.082682388124423</v>
       </c>
       <c r="E56">
-        <v>-18.05235614562479</v>
+        <v>-24.39922530565316</v>
       </c>
       <c r="F56">
-        <v>-1.322980756054181</v>
+        <v>-1.103499842478036</v>
       </c>
       <c r="G56">
-        <v>-8.538815117563104</v>
+        <v>-12.23283769937577</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.245784658652161</v>
       </c>
       <c r="E57">
-        <v>-17.8515092664366</v>
+        <v>-25.05548723037074</v>
       </c>
       <c r="F57">
-        <v>-1.434185766410404</v>
+        <v>-0.8029822309882225</v>
       </c>
       <c r="G57">
-        <v>-9.784235728345845</v>
+        <v>-12.65791836770927</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.286642811373188</v>
       </c>
       <c r="E58">
-        <v>-17.10145811654615</v>
+        <v>-24.24697800951528</v>
       </c>
       <c r="F58">
-        <v>-1.870723790542104</v>
+        <v>-1.128188504551072</v>
       </c>
       <c r="G58">
-        <v>-9.296483122408404</v>
+        <v>-13.08338305932532</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.218521348287613</v>
       </c>
       <c r="E59">
-        <v>-16.97343362787531</v>
+        <v>-24.03496844189818</v>
       </c>
       <c r="F59">
-        <v>-1.926205354079407</v>
+        <v>-0.9743118041744386</v>
       </c>
       <c r="G59">
-        <v>-9.596646975908582</v>
+        <v>-12.77442970741838</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.056541397846315</v>
       </c>
       <c r="E60">
-        <v>-16.45615057045313</v>
+        <v>-22.9768316198439</v>
       </c>
       <c r="F60">
-        <v>-1.88439019595349</v>
+        <v>-1.243518784573236</v>
       </c>
       <c r="G60">
-        <v>-9.422813540186992</v>
+        <v>-13.4912985490377</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.818000412958879</v>
       </c>
       <c r="E61">
-        <v>-16.1615869216762</v>
+        <v>-23.11189788559668</v>
       </c>
       <c r="F61">
-        <v>-1.904530292617755</v>
+        <v>-1.188966649261874</v>
       </c>
       <c r="G61">
-        <v>-9.447003696442447</v>
+        <v>-13.25975568347553</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.520328557997532</v>
       </c>
       <c r="E62">
-        <v>-15.8159783138848</v>
+        <v>-23.12292471980535</v>
       </c>
       <c r="F62">
-        <v>-1.808161342445672</v>
+        <v>-1.206678801068534</v>
       </c>
       <c r="G62">
-        <v>-9.598408186135476</v>
+        <v>-12.90003180517833</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.184862476197023</v>
       </c>
       <c r="E63">
-        <v>-15.66475445287266</v>
+        <v>-23.14324851115178</v>
       </c>
       <c r="F63">
-        <v>-1.835769171246173</v>
+        <v>-1.379639429670862</v>
       </c>
       <c r="G63">
-        <v>-10.02881552224166</v>
+        <v>-13.27850330286443</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.827356609290697</v>
       </c>
       <c r="E64">
-        <v>-15.44074442913523</v>
+        <v>-22.29494306071691</v>
       </c>
       <c r="F64">
-        <v>-1.654565458618587</v>
+        <v>-1.477487015656942</v>
       </c>
       <c r="G64">
-        <v>-9.699204366169665</v>
+        <v>-13.42414413277358</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.458729477311391</v>
       </c>
       <c r="E65">
-        <v>-15.59700848171791</v>
+        <v>-23.10086199443998</v>
       </c>
       <c r="F65">
-        <v>-2.102773522720927</v>
+        <v>-1.483307125029012</v>
       </c>
       <c r="G65">
-        <v>-9.773976347719644</v>
+        <v>-13.68339295395391</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.094459593768152</v>
       </c>
       <c r="E66">
-        <v>-14.44822066697808</v>
+        <v>-21.99571508371208</v>
       </c>
       <c r="F66">
-        <v>-1.938534774502674</v>
+        <v>-1.409237825340291</v>
       </c>
       <c r="G66">
-        <v>-9.751775829333292</v>
+        <v>-13.25530299972521</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.739000521180913</v>
       </c>
       <c r="E67">
-        <v>-14.8768497887521</v>
+        <v>-22.53618392805353</v>
       </c>
       <c r="F67">
-        <v>-2.253152027555538</v>
+        <v>-1.586549867909525</v>
       </c>
       <c r="G67">
-        <v>-9.693242073653437</v>
+        <v>-13.14720706677693</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.390073035301094</v>
       </c>
       <c r="E68">
-        <v>-16.04960681641452</v>
+        <v>-22.65272420664092</v>
       </c>
       <c r="F68">
-        <v>-2.404512147762466</v>
+        <v>-1.692743255478811</v>
       </c>
       <c r="G68">
-        <v>-9.895112519547116</v>
+        <v>-13.58179727717199</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.050983899709581</v>
       </c>
       <c r="E69">
-        <v>-15.10722231847031</v>
+        <v>-22.02954731302338</v>
       </c>
       <c r="F69">
-        <v>-2.135071567756079</v>
+        <v>-1.842223810048787</v>
       </c>
       <c r="G69">
-        <v>-9.549239963786219</v>
+        <v>-13.58685744602876</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.714936490554077</v>
       </c>
       <c r="E70">
-        <v>-15.02530222367155</v>
+        <v>-21.97260628085094</v>
       </c>
       <c r="F70">
-        <v>-2.426993210707042</v>
+        <v>-1.916660904864351</v>
       </c>
       <c r="G70">
-        <v>-9.825091170845992</v>
+        <v>-12.96676578215896</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.369545916883267</v>
       </c>
       <c r="E71">
-        <v>-15.55002103541432</v>
+        <v>-22.06842879085324</v>
       </c>
       <c r="F71">
-        <v>-2.450721794960234</v>
+        <v>-2.062659002872958</v>
       </c>
       <c r="G71">
-        <v>-9.372019839977954</v>
+        <v>-13.06231805805894</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.011530744833212</v>
       </c>
       <c r="E72">
-        <v>-14.86719055369374</v>
+        <v>-22.60003088308767</v>
       </c>
       <c r="F72">
-        <v>-2.477493801051311</v>
+        <v>-1.981394503923521</v>
       </c>
       <c r="G72">
-        <v>-9.696479787190844</v>
+        <v>-12.72718491202744</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.632718270740533</v>
       </c>
       <c r="E73">
-        <v>-15.45404002882175</v>
+        <v>-21.91574676121063</v>
       </c>
       <c r="F73">
-        <v>-2.624976333445735</v>
+        <v>-1.82300899977345</v>
       </c>
       <c r="G73">
-        <v>-9.449662064510482</v>
+        <v>-13.15896281398688</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.222215340686967</v>
       </c>
       <c r="E74">
-        <v>-15.71807723431298</v>
+        <v>-22.59297552058372</v>
       </c>
       <c r="F74">
-        <v>-2.420719155998239</v>
+        <v>-2.148391715593096</v>
       </c>
       <c r="G74">
-        <v>-9.660345182629699</v>
+        <v>-13.03791602688897</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.781231874379565</v>
       </c>
       <c r="E75">
-        <v>-16.70443321487167</v>
+        <v>-22.32095914389098</v>
       </c>
       <c r="F75">
-        <v>-2.453207725536035</v>
+        <v>-2.121812719106871</v>
       </c>
       <c r="G75">
-        <v>-8.871372659165051</v>
+        <v>-13.01104763929225</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.310216494298418</v>
       </c>
       <c r="E76">
-        <v>-15.84022829219588</v>
+        <v>-22.59826930669869</v>
       </c>
       <c r="F76">
-        <v>-2.55356277965039</v>
+        <v>-2.254515520300546</v>
       </c>
       <c r="G76">
-        <v>-8.799027307495358</v>
+        <v>-12.01478861743167</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.808940212524423</v>
       </c>
       <c r="E77">
-        <v>-16.13788488872005</v>
+        <v>-23.00669237745048</v>
       </c>
       <c r="F77">
-        <v>-2.927406645268612</v>
+        <v>-2.153429846136922</v>
       </c>
       <c r="G77">
-        <v>-8.609630997193653</v>
+        <v>-12.45092981841188</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.289281369473507</v>
       </c>
       <c r="E78">
-        <v>-16.6559785429896</v>
+        <v>-23.97813156462791</v>
       </c>
       <c r="F78">
-        <v>-2.751975825071136</v>
+        <v>-2.21517138213718</v>
       </c>
       <c r="G78">
-        <v>-8.739126296507784</v>
+        <v>-12.09034850882</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.7640959324408629</v>
       </c>
       <c r="E79">
-        <v>-18.07652913987774</v>
+        <v>-23.14853324031873</v>
       </c>
       <c r="F79">
-        <v>-2.625865171668939</v>
+        <v>-2.467399315880797</v>
       </c>
       <c r="G79">
-        <v>-8.285608041991948</v>
+        <v>-12.24192845742661</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.2429917481397421</v>
       </c>
       <c r="E80">
-        <v>-18.06048475646856</v>
+        <v>-24.06256949097493</v>
       </c>
       <c r="F80">
-        <v>-2.602224394360444</v>
+        <v>-2.490201785377658</v>
       </c>
       <c r="G80">
-        <v>-8.414331984195428</v>
+        <v>-11.99090634191137</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.2568906942521206</v>
       </c>
       <c r="E81">
-        <v>-18.99027103972344</v>
+        <v>-23.42255120252286</v>
       </c>
       <c r="F81">
-        <v>-2.496022723117131</v>
+        <v>-2.548716830344012</v>
       </c>
       <c r="G81">
-        <v>-8.018125894055453</v>
+        <v>-12.10935104021541</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.7198683651759421</v>
       </c>
       <c r="E82">
-        <v>-19.07659281125765</v>
+        <v>-25.30887346499593</v>
       </c>
       <c r="F82">
-        <v>-2.808186351922902</v>
+        <v>-2.630705322403497</v>
       </c>
       <c r="G82">
-        <v>-7.022833551492345</v>
+        <v>-11.47226965663807</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.135785577353948</v>
       </c>
       <c r="E83">
-        <v>-19.63440571104848</v>
+        <v>-25.8337145455369</v>
       </c>
       <c r="F83">
-        <v>-2.72737911177981</v>
+        <v>-2.707245642054768</v>
       </c>
       <c r="G83">
-        <v>-7.447960567463394</v>
+        <v>-11.2228299818906</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.490853531522853</v>
       </c>
       <c r="E84">
-        <v>-20.93457588339071</v>
+        <v>-25.82281450860044</v>
       </c>
       <c r="F84">
-        <v>-3.162121235382241</v>
+        <v>-2.481175894156755</v>
       </c>
       <c r="G84">
-        <v>-7.133856006697344</v>
+        <v>-11.44700688362789</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.774013123855446</v>
       </c>
       <c r="E85">
-        <v>-20.46547126093614</v>
+        <v>-27.23261450819437</v>
       </c>
       <c r="F85">
-        <v>-2.708581798675484</v>
+        <v>-2.858804570438368</v>
       </c>
       <c r="G85">
-        <v>-7.242905376760937</v>
+        <v>-11.58947621091042</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.97892960645398</v>
       </c>
       <c r="E86">
-        <v>-22.59635829066745</v>
+        <v>-27.35570748867087</v>
       </c>
       <c r="F86">
-        <v>-2.986616690485915</v>
+        <v>-2.884228822765091</v>
       </c>
       <c r="G86">
-        <v>-7.185053593462173</v>
+        <v>-11.47098516496883</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.098315431218418</v>
       </c>
       <c r="E87">
-        <v>-23.72097763962834</v>
+        <v>-28.84711058988301</v>
       </c>
       <c r="F87">
-        <v>-2.757289801960094</v>
+        <v>-2.801841057617457</v>
       </c>
       <c r="G87">
-        <v>-6.979895775847997</v>
+        <v>-10.73477611630909</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.128891709772258</v>
       </c>
       <c r="E88">
-        <v>-24.12273026816683</v>
+        <v>-29.644712981091</v>
       </c>
       <c r="F88">
-        <v>-3.371510977257483</v>
+        <v>-2.953484479476144</v>
       </c>
       <c r="G88">
-        <v>-7.515975725567721</v>
+        <v>-11.39357798916959</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.06914827301651</v>
       </c>
       <c r="E89">
-        <v>-25.74662293342139</v>
+        <v>-30.7026256436819</v>
       </c>
       <c r="F89">
-        <v>-3.333926291457664</v>
+        <v>-2.95458123791745</v>
       </c>
       <c r="G89">
-        <v>-7.225717024321041</v>
+        <v>-10.93101532424046</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.918466732779097</v>
       </c>
       <c r="E90">
-        <v>-26.85316008566965</v>
+        <v>-31.00938220872448</v>
       </c>
       <c r="F90">
-        <v>-3.078318618710626</v>
+        <v>-3.165386659684077</v>
       </c>
       <c r="G90">
-        <v>-7.363799878764041</v>
+        <v>-11.66246711896028</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.681363875076352</v>
       </c>
       <c r="E91">
-        <v>-29.01966356347128</v>
+        <v>-32.99537618410637</v>
       </c>
       <c r="F91">
-        <v>-3.028672903526046</v>
+        <v>-3.132405211541614</v>
       </c>
       <c r="G91">
-        <v>-7.043269549106266</v>
+        <v>-11.12348382080261</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.360453607169464</v>
       </c>
       <c r="E92">
-        <v>-30.23827139046137</v>
+        <v>-34.95260755682854</v>
       </c>
       <c r="F92">
-        <v>-3.441458320749873</v>
+        <v>-3.257280769146237</v>
       </c>
       <c r="G92">
-        <v>-7.269396362166185</v>
+        <v>-11.66352980407838</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.9610793895145775</v>
       </c>
       <c r="E93">
-        <v>-32.06614690315444</v>
+        <v>-36.27001536548098</v>
       </c>
       <c r="F93">
-        <v>-3.022098151450026</v>
+        <v>-3.532740266701365</v>
       </c>
       <c r="G93">
-        <v>-7.249539710021636</v>
+        <v>-11.01197471540334</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.4954816144929944</v>
       </c>
       <c r="E94">
-        <v>-33.21110136464677</v>
+        <v>-37.18052619912221</v>
       </c>
       <c r="F94">
-        <v>-3.179475532470891</v>
+        <v>-3.529005158082142</v>
       </c>
       <c r="G94">
-        <v>-7.659504427422823</v>
+        <v>-11.68594219737925</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.02564845835710819</v>
       </c>
       <c r="E95">
-        <v>-36.0375982297483</v>
+        <v>-38.45107788721727</v>
       </c>
       <c r="F95">
-        <v>-3.224147729769062</v>
+        <v>-3.380058072119569</v>
       </c>
       <c r="G95">
-        <v>-7.307325282409614</v>
+        <v>-11.52076914878839</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.5907095118572208</v>
       </c>
       <c r="E96">
-        <v>-36.7723295520708</v>
+        <v>-40.6060654556174</v>
       </c>
       <c r="F96">
-        <v>-3.477981867906706</v>
+        <v>-3.811335963243492</v>
       </c>
       <c r="G96">
-        <v>-8.287978392598065</v>
+        <v>-11.5454360236015</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.172257357523113</v>
       </c>
       <c r="E97">
-        <v>-38.71652571236189</v>
+        <v>-42.05976221800469</v>
       </c>
       <c r="F97">
-        <v>-3.461875092126673</v>
+        <v>-3.912411696998282</v>
       </c>
       <c r="G97">
-        <v>-8.552388354274115</v>
+        <v>-12.4012285982308</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.764411859452069</v>
       </c>
       <c r="E98">
-        <v>-41.62181123248588</v>
+        <v>-43.86374097335928</v>
       </c>
       <c r="F98">
-        <v>-3.659579055050623</v>
+        <v>-3.88700235528481</v>
       </c>
       <c r="G98">
-        <v>-8.463477032725908</v>
+        <v>-12.42263789623326</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.334996805880239</v>
       </c>
       <c r="E99">
-        <v>-43.1129607391536</v>
+        <v>-45.6058653022431</v>
       </c>
       <c r="F99">
-        <v>-3.697524909038062</v>
+        <v>-3.828737477274101</v>
       </c>
       <c r="G99">
-        <v>-8.814590182075472</v>
+        <v>-12.49408277951628</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.892333919249441</v>
       </c>
       <c r="E100">
-        <v>-45.36171489035655</v>
+        <v>-47.90810978842465</v>
       </c>
       <c r="F100">
-        <v>-3.483913806878154</v>
+        <v>-4.25584785199454</v>
       </c>
       <c r="G100">
-        <v>-8.671233628588412</v>
+        <v>-13.46083821953087</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.389934997793906</v>
       </c>
       <c r="E101">
-        <v>-47.15774164535367</v>
+        <v>-48.99649681685017</v>
       </c>
       <c r="F101">
-        <v>-3.695802733207642</v>
+        <v>-4.310394188734082</v>
       </c>
       <c r="G101">
-        <v>-9.48241991262157</v>
+        <v>-12.93972855673973</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.893082781586499</v>
       </c>
       <c r="E102">
-        <v>-49.52692829855362</v>
+        <v>-51.22163950457713</v>
       </c>
       <c r="F102">
-        <v>-3.600226530640038</v>
+        <v>-4.385570187272942</v>
       </c>
       <c r="G102">
-        <v>-9.916104688811634</v>
+        <v>-13.52022609595985</v>
       </c>
     </row>
   </sheetData>
